--- a/data/8.Dentistas/dentista_madrid.xlsx
+++ b/data/8.Dentistas/dentista_madrid.xlsx
@@ -1,20 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/06ae8d044cc0a8d9/Documentos/GitHub/Leads_sheacher/data/8.Dentistas/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_800DDBE284F5D7EE86170B46ABDBC66740AFAC21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{93DC4408-EA8D-44DC-9CE5-6853A8F5EBCB}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Generated by Outscraper ©" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Generated by Outscraper ©'!$A$1:$DH$77</definedName>
+  </definedNames>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4307" uniqueCount="1398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4360" uniqueCount="1398">
   <si>
     <t>query</t>
   </si>
@@ -4213,8 +4223,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4277,13 +4287,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4321,7 +4339,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -4355,6 +4373,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -4389,9 +4408,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4564,11 +4584,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DH77"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:112">
+    <row r="1" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4906,7 +4926,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="2" spans="1:112">
+    <row r="2" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>112</v>
       </c>
@@ -4998,10 +5018,10 @@
         <v>653</v>
       </c>
       <c r="AT2">
-        <v>40.4097344</v>
+        <v>40.409734399999998</v>
       </c>
       <c r="AU2">
-        <v>-3.7095532</v>
+        <v>-3.7095532000000002</v>
       </c>
       <c r="AV2" t="s">
         <v>689</v>
@@ -5013,7 +5033,7 @@
         <v>0</v>
       </c>
       <c r="AZ2">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA2">
         <v>506</v>
@@ -5109,7 +5129,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="3" spans="1:112">
+    <row r="3" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>112</v>
       </c>
@@ -5201,10 +5221,10 @@
         <v>654</v>
       </c>
       <c r="AT3">
-        <v>40.4097344</v>
+        <v>40.409734399999998</v>
       </c>
       <c r="AU3">
-        <v>-3.7095532</v>
+        <v>-3.7095532000000002</v>
       </c>
       <c r="AV3" t="s">
         <v>689</v>
@@ -5216,7 +5236,7 @@
         <v>0</v>
       </c>
       <c r="AZ3">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA3">
         <v>506</v>
@@ -5312,7 +5332,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="4" spans="1:112">
+    <row r="4" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -5389,7 +5409,7 @@
         <v>240</v>
       </c>
       <c r="AT4">
-        <v>40.4634956</v>
+        <v>40.463495600000002</v>
       </c>
       <c r="AU4">
         <v>-3.7170481</v>
@@ -5404,7 +5424,7 @@
         <v>0</v>
       </c>
       <c r="AZ4">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA4">
         <v>211</v>
@@ -5491,7 +5511,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="5" spans="1:112">
+    <row r="5" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>112</v>
       </c>
@@ -5592,10 +5612,10 @@
         <v>655</v>
       </c>
       <c r="AT5">
-        <v>40.4343653</v>
+        <v>40.434365300000003</v>
       </c>
       <c r="AU5">
-        <v>-3.7041189</v>
+        <v>-3.7041189000000001</v>
       </c>
       <c r="AV5" t="s">
         <v>691</v>
@@ -5607,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="AZ5">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA5">
         <v>318</v>
@@ -5730,7 +5750,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="6" spans="1:112">
+    <row r="6" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>112</v>
       </c>
@@ -5831,10 +5851,10 @@
         <v>656</v>
       </c>
       <c r="AT6">
-        <v>40.4343653</v>
+        <v>40.434365300000003</v>
       </c>
       <c r="AU6">
-        <v>-3.7041189</v>
+        <v>-3.7041189000000001</v>
       </c>
       <c r="AV6" t="s">
         <v>691</v>
@@ -5846,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="AZ6">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA6">
         <v>318</v>
@@ -5969,7 +5989,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="7" spans="1:112">
+    <row r="7" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>112</v>
       </c>
@@ -6073,7 +6093,7 @@
         <v>657</v>
       </c>
       <c r="AT7">
-        <v>40.3879872</v>
+        <v>40.387987199999998</v>
       </c>
       <c r="AU7">
         <v>-3.7001963</v>
@@ -6202,7 +6222,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="8" spans="1:112">
+    <row r="8" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>112</v>
       </c>
@@ -6306,7 +6326,7 @@
         <v>658</v>
       </c>
       <c r="AT8">
-        <v>40.3879872</v>
+        <v>40.387987199999998</v>
       </c>
       <c r="AU8">
         <v>-3.7001963</v>
@@ -6435,7 +6455,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="9" spans="1:112">
+    <row r="9" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -6533,10 +6553,10 @@
         <v>659</v>
       </c>
       <c r="AT9">
-        <v>40.4117736</v>
+        <v>40.411773599999997</v>
       </c>
       <c r="AU9">
-        <v>-3.7065859</v>
+        <v>-3.7065858999999999</v>
       </c>
       <c r="AV9" t="s">
         <v>693</v>
@@ -6548,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="AZ9">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA9">
         <v>847</v>
@@ -6680,7 +6700,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="10" spans="1:112">
+    <row r="10" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>112</v>
       </c>
@@ -6778,10 +6798,10 @@
         <v>659</v>
       </c>
       <c r="AT10">
-        <v>40.4117736</v>
+        <v>40.411773599999997</v>
       </c>
       <c r="AU10">
-        <v>-3.7065859</v>
+        <v>-3.7065858999999999</v>
       </c>
       <c r="AV10" t="s">
         <v>693</v>
@@ -6793,7 +6813,7 @@
         <v>0</v>
       </c>
       <c r="AZ10">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA10">
         <v>847</v>
@@ -6925,7 +6945,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="11" spans="1:112">
+    <row r="11" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>112</v>
       </c>
@@ -7023,10 +7043,10 @@
         <v>659</v>
       </c>
       <c r="AT11">
-        <v>40.4117736</v>
+        <v>40.411773599999997</v>
       </c>
       <c r="AU11">
-        <v>-3.7065859</v>
+        <v>-3.7065858999999999</v>
       </c>
       <c r="AV11" t="s">
         <v>693</v>
@@ -7038,7 +7058,7 @@
         <v>0</v>
       </c>
       <c r="AZ11">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA11">
         <v>847</v>
@@ -7170,7 +7190,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="12" spans="1:112">
+    <row r="12" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>112</v>
       </c>
@@ -7217,10 +7237,10 @@
         <v>390</v>
       </c>
       <c r="AT12">
-        <v>40.430435</v>
+        <v>40.430435000000003</v>
       </c>
       <c r="AU12">
-        <v>-3.7043698</v>
+        <v>-3.7043697999999998</v>
       </c>
       <c r="AV12" t="s">
         <v>694</v>
@@ -7304,7 +7324,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="13" spans="1:112">
+    <row r="13" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>112</v>
       </c>
@@ -7354,7 +7374,7 @@
         <v>40.4590338</v>
       </c>
       <c r="AU13">
-        <v>-3.7115053</v>
+        <v>-3.7115052999999998</v>
       </c>
       <c r="AV13" t="s">
         <v>695</v>
@@ -7438,7 +7458,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="14" spans="1:112">
+    <row r="14" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>112</v>
       </c>
@@ -7485,7 +7505,7 @@
         <v>390</v>
       </c>
       <c r="AT14">
-        <v>40.4387968</v>
+        <v>40.438796799999999</v>
       </c>
       <c r="AU14">
         <v>-3.7168161</v>
@@ -7572,7 +7592,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="15" spans="1:112">
+    <row r="15" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>112</v>
       </c>
@@ -7652,10 +7672,10 @@
         <v>244</v>
       </c>
       <c r="AT15">
-        <v>40.3709151</v>
+        <v>40.370915099999998</v>
       </c>
       <c r="AU15">
-        <v>-3.7531614</v>
+        <v>-3.7531614000000002</v>
       </c>
       <c r="AV15" t="s">
         <v>697</v>
@@ -7751,7 +7771,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="16" spans="1:112">
+    <row r="16" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>112</v>
       </c>
@@ -7831,10 +7851,10 @@
         <v>660</v>
       </c>
       <c r="AT16">
-        <v>40.3709151</v>
+        <v>40.370915099999998</v>
       </c>
       <c r="AU16">
-        <v>-3.7531614</v>
+        <v>-3.7531614000000002</v>
       </c>
       <c r="AV16" t="s">
         <v>697</v>
@@ -7930,7 +7950,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="17" spans="1:111">
+    <row r="17" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>112</v>
       </c>
@@ -8010,10 +8030,10 @@
         <v>661</v>
       </c>
       <c r="AT17">
-        <v>40.3709151</v>
+        <v>40.370915099999998</v>
       </c>
       <c r="AU17">
-        <v>-3.7531614</v>
+        <v>-3.7531614000000002</v>
       </c>
       <c r="AV17" t="s">
         <v>697</v>
@@ -8109,7 +8129,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="18" spans="1:111">
+    <row r="18" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>112</v>
       </c>
@@ -8159,7 +8179,7 @@
         <v>40.3872328</v>
       </c>
       <c r="AU18">
-        <v>-3.7030283</v>
+        <v>-3.7030283000000002</v>
       </c>
       <c r="AV18" t="s">
         <v>698</v>
@@ -8243,7 +8263,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="19" spans="1:111">
+    <row r="19" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>112</v>
       </c>
@@ -8338,10 +8358,10 @@
         <v>662</v>
       </c>
       <c r="AT19">
-        <v>40.4436974</v>
+        <v>40.443697399999998</v>
       </c>
       <c r="AU19">
-        <v>-3.6974743</v>
+        <v>-3.6974743000000001</v>
       </c>
       <c r="AV19" t="s">
         <v>699</v>
@@ -8458,7 +8478,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="20" spans="1:111">
+    <row r="20" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>112</v>
       </c>
@@ -8553,10 +8573,10 @@
         <v>663</v>
       </c>
       <c r="AT20">
-        <v>40.4436974</v>
+        <v>40.443697399999998</v>
       </c>
       <c r="AU20">
-        <v>-3.6974743</v>
+        <v>-3.6974743000000001</v>
       </c>
       <c r="AV20" t="s">
         <v>699</v>
@@ -8673,7 +8693,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="21" spans="1:111">
+    <row r="21" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>112</v>
       </c>
@@ -8921,7 +8941,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="22" spans="1:111">
+    <row r="22" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>112</v>
       </c>
@@ -9169,7 +9189,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="23" spans="1:111">
+    <row r="23" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>112</v>
       </c>
@@ -9417,7 +9437,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="24" spans="1:111">
+    <row r="24" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>112</v>
       </c>
@@ -9497,10 +9517,10 @@
         <v>665</v>
       </c>
       <c r="AT24">
-        <v>40.481795</v>
+        <v>40.481794999999998</v>
       </c>
       <c r="AU24">
-        <v>-3.7234217</v>
+        <v>-3.7234216999999998</v>
       </c>
       <c r="AV24" t="s">
         <v>701</v>
@@ -9602,7 +9622,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="25" spans="1:111">
+    <row r="25" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>112</v>
       </c>
@@ -9691,10 +9711,10 @@
         <v>666</v>
       </c>
       <c r="AT25">
-        <v>40.456526</v>
+        <v>40.456525999999997</v>
       </c>
       <c r="AU25">
-        <v>-3.692746</v>
+        <v>-3.6927460000000001</v>
       </c>
       <c r="AV25" t="s">
         <v>702</v>
@@ -9808,7 +9828,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="26" spans="1:111">
+    <row r="26" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>112</v>
       </c>
@@ -9897,10 +9917,10 @@
         <v>667</v>
       </c>
       <c r="AT26">
-        <v>40.456526</v>
+        <v>40.456525999999997</v>
       </c>
       <c r="AU26">
-        <v>-3.692746</v>
+        <v>-3.6927460000000001</v>
       </c>
       <c r="AV26" t="s">
         <v>702</v>
@@ -10014,7 +10034,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="27" spans="1:111">
+    <row r="27" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>112</v>
       </c>
@@ -10103,10 +10123,10 @@
         <v>668</v>
       </c>
       <c r="AT27">
-        <v>40.456526</v>
+        <v>40.456525999999997</v>
       </c>
       <c r="AU27">
-        <v>-3.692746</v>
+        <v>-3.6927460000000001</v>
       </c>
       <c r="AV27" t="s">
         <v>702</v>
@@ -10220,7 +10240,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="28" spans="1:111">
+    <row r="28" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>112</v>
       </c>
@@ -10321,7 +10341,7 @@
         <v>658</v>
       </c>
       <c r="AT28">
-        <v>40.4057845</v>
+        <v>40.405784500000003</v>
       </c>
       <c r="AU28">
         <v>-3.6947041</v>
@@ -10336,7 +10356,7 @@
         <v>0</v>
       </c>
       <c r="AZ28">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA28">
         <v>1636</v>
@@ -10471,7 +10491,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="29" spans="1:111">
+    <row r="29" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>112</v>
       </c>
@@ -10572,7 +10592,7 @@
         <v>669</v>
       </c>
       <c r="AT29">
-        <v>40.4057845</v>
+        <v>40.405784500000003</v>
       </c>
       <c r="AU29">
         <v>-3.6947041</v>
@@ -10587,7 +10607,7 @@
         <v>0</v>
       </c>
       <c r="AZ29">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA29">
         <v>1636</v>
@@ -10722,7 +10742,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="30" spans="1:111">
+    <row r="30" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>112</v>
       </c>
@@ -10820,10 +10840,10 @@
         <v>670</v>
       </c>
       <c r="AT30">
-        <v>40.4536308</v>
+        <v>40.453630799999999</v>
       </c>
       <c r="AU30">
-        <v>-3.7035397</v>
+        <v>-3.7035396999999999</v>
       </c>
       <c r="AV30" t="s">
         <v>704</v>
@@ -10889,7 +10909,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="31" spans="1:111">
+    <row r="31" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>112</v>
       </c>
@@ -10987,10 +11007,10 @@
         <v>658</v>
       </c>
       <c r="AT31">
-        <v>40.4536308</v>
+        <v>40.453630799999999</v>
       </c>
       <c r="AU31">
-        <v>-3.7035397</v>
+        <v>-3.7035396999999999</v>
       </c>
       <c r="AV31" t="s">
         <v>704</v>
@@ -11056,7 +11076,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="32" spans="1:111">
+    <row r="32" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>112</v>
       </c>
@@ -11154,10 +11174,10 @@
         <v>671</v>
       </c>
       <c r="AT32">
-        <v>40.4536308</v>
+        <v>40.453630799999999</v>
       </c>
       <c r="AU32">
-        <v>-3.7035397</v>
+        <v>-3.7035396999999999</v>
       </c>
       <c r="AV32" t="s">
         <v>704</v>
@@ -11223,7 +11243,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="33" spans="1:111">
+    <row r="33" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>112</v>
       </c>
@@ -11312,7 +11332,7 @@
         <v>672</v>
       </c>
       <c r="AT33">
-        <v>40.4378132</v>
+        <v>40.437813200000001</v>
       </c>
       <c r="AU33">
         <v>-3.7011968</v>
@@ -11423,7 +11443,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="34" spans="1:111">
+    <row r="34" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>112</v>
       </c>
@@ -11518,10 +11538,10 @@
         <v>662</v>
       </c>
       <c r="AT34">
-        <v>40.481061</v>
+        <v>40.481060999999997</v>
       </c>
       <c r="AU34">
-        <v>-3.7213329</v>
+        <v>-3.7213329000000002</v>
       </c>
       <c r="AV34" t="s">
         <v>701</v>
@@ -11644,7 +11664,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="35" spans="1:111">
+    <row r="35" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>112</v>
       </c>
@@ -11739,10 +11759,10 @@
         <v>663</v>
       </c>
       <c r="AT35">
-        <v>40.481061</v>
+        <v>40.481060999999997</v>
       </c>
       <c r="AU35">
-        <v>-3.7213329</v>
+        <v>-3.7213329000000002</v>
       </c>
       <c r="AV35" t="s">
         <v>701</v>
@@ -11865,7 +11885,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="36" spans="1:111">
+    <row r="36" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>112</v>
       </c>
@@ -11945,10 +11965,10 @@
         <v>673</v>
       </c>
       <c r="AT36">
-        <v>40.3875149</v>
+        <v>40.387514899999999</v>
       </c>
       <c r="AU36">
-        <v>-3.7288233</v>
+        <v>-3.7288233000000002</v>
       </c>
       <c r="AV36" t="s">
         <v>706</v>
@@ -12041,7 +12061,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="37" spans="1:111">
+    <row r="37" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>112</v>
       </c>
@@ -12127,10 +12147,10 @@
         <v>674</v>
       </c>
       <c r="AT37">
-        <v>40.392553</v>
+        <v>40.392552999999999</v>
       </c>
       <c r="AU37">
-        <v>-3.6801418</v>
+        <v>-3.6801417999999999</v>
       </c>
       <c r="AV37" t="s">
         <v>707</v>
@@ -12274,7 +12294,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="38" spans="1:111">
+    <row r="38" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>112</v>
       </c>
@@ -12360,10 +12380,10 @@
         <v>674</v>
       </c>
       <c r="AT38">
-        <v>40.392553</v>
+        <v>40.392552999999999</v>
       </c>
       <c r="AU38">
-        <v>-3.6801418</v>
+        <v>-3.6801417999999999</v>
       </c>
       <c r="AV38" t="s">
         <v>707</v>
@@ -12507,7 +12527,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="39" spans="1:111">
+    <row r="39" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>112</v>
       </c>
@@ -12593,10 +12613,10 @@
         <v>675</v>
       </c>
       <c r="AT39">
-        <v>40.392553</v>
+        <v>40.392552999999999</v>
       </c>
       <c r="AU39">
-        <v>-3.6801418</v>
+        <v>-3.6801417999999999</v>
       </c>
       <c r="AV39" t="s">
         <v>707</v>
@@ -12740,7 +12760,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="40" spans="1:111">
+    <row r="40" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>112</v>
       </c>
@@ -12841,7 +12861,7 @@
         <v>40.4594539</v>
       </c>
       <c r="AU40">
-        <v>-3.6958064</v>
+        <v>-3.6958063999999999</v>
       </c>
       <c r="AV40" t="s">
         <v>708</v>
@@ -12853,7 +12873,7 @@
         <v>0</v>
       </c>
       <c r="AZ40">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA40">
         <v>39</v>
@@ -12949,7 +12969,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="41" spans="1:111">
+    <row r="41" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>112</v>
       </c>
@@ -13050,7 +13070,7 @@
         <v>40.4594539</v>
       </c>
       <c r="AU41">
-        <v>-3.6958064</v>
+        <v>-3.6958063999999999</v>
       </c>
       <c r="AV41" t="s">
         <v>708</v>
@@ -13062,7 +13082,7 @@
         <v>0</v>
       </c>
       <c r="AZ41">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA41">
         <v>39</v>
@@ -13158,7 +13178,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="42" spans="1:111">
+    <row r="42" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>112</v>
       </c>
@@ -13199,10 +13219,10 @@
         <v>390</v>
       </c>
       <c r="AT42">
-        <v>40.4225533</v>
+        <v>40.422553299999997</v>
       </c>
       <c r="AU42">
-        <v>-3.6542357</v>
+        <v>-3.6542357000000001</v>
       </c>
       <c r="AV42" t="s">
         <v>709</v>
@@ -13286,7 +13306,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="43" spans="1:111">
+    <row r="43" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>112</v>
       </c>
@@ -13378,10 +13398,10 @@
         <v>677</v>
       </c>
       <c r="AT43">
-        <v>40.4600591</v>
+        <v>40.460059100000002</v>
       </c>
       <c r="AU43">
-        <v>-3.6917284</v>
+        <v>-3.6917284000000001</v>
       </c>
       <c r="AV43" t="s">
         <v>710</v>
@@ -13495,7 +13515,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="44" spans="1:111">
+    <row r="44" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>112</v>
       </c>
@@ -13587,10 +13607,10 @@
         <v>678</v>
       </c>
       <c r="AT44">
-        <v>40.4814197</v>
+        <v>40.481419699999996</v>
       </c>
       <c r="AU44">
-        <v>-3.723715</v>
+        <v>-3.7237149999999999</v>
       </c>
       <c r="AV44" t="s">
         <v>701</v>
@@ -13602,7 +13622,7 @@
         <v>0</v>
       </c>
       <c r="AZ44">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA44">
         <v>444</v>
@@ -13704,7 +13724,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="45" spans="1:111">
+    <row r="45" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>112</v>
       </c>
@@ -13796,10 +13816,10 @@
         <v>665</v>
       </c>
       <c r="AT45">
-        <v>40.4814197</v>
+        <v>40.481419699999996</v>
       </c>
       <c r="AU45">
-        <v>-3.723715</v>
+        <v>-3.7237149999999999</v>
       </c>
       <c r="AV45" t="s">
         <v>701</v>
@@ -13811,7 +13831,7 @@
         <v>0</v>
       </c>
       <c r="AZ45">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA45">
         <v>444</v>
@@ -13913,7 +13933,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="46" spans="1:111">
+    <row r="46" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>112</v>
       </c>
@@ -13963,10 +13983,10 @@
         <v>390</v>
       </c>
       <c r="AT46">
-        <v>40.4333801</v>
+        <v>40.433380100000001</v>
       </c>
       <c r="AU46">
-        <v>-3.6935382</v>
+        <v>-3.6935381999999999</v>
       </c>
       <c r="AV46" t="s">
         <v>711</v>
@@ -14068,7 +14088,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="47" spans="1:111">
+    <row r="47" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>112</v>
       </c>
@@ -14163,7 +14183,7 @@
         <v>679</v>
       </c>
       <c r="AT47">
-        <v>40.3719954</v>
+        <v>40.371995400000003</v>
       </c>
       <c r="AU47">
         <v>-3.7608199</v>
@@ -14319,7 +14339,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="48" spans="1:111">
+    <row r="48" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>112</v>
       </c>
@@ -14414,7 +14434,7 @@
         <v>679</v>
       </c>
       <c r="AT48">
-        <v>40.3719954</v>
+        <v>40.371995400000003</v>
       </c>
       <c r="AU48">
         <v>-3.7608199</v>
@@ -14570,7 +14590,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="49" spans="1:111">
+    <row r="49" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>112</v>
       </c>
@@ -14665,7 +14685,7 @@
         <v>679</v>
       </c>
       <c r="AT49">
-        <v>40.3719954</v>
+        <v>40.371995400000003</v>
       </c>
       <c r="AU49">
         <v>-3.7608199</v>
@@ -14821,7 +14841,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="50" spans="1:111">
+    <row r="50" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>112</v>
       </c>
@@ -14901,10 +14921,10 @@
         <v>680</v>
       </c>
       <c r="AT50">
-        <v>40.4817839</v>
+        <v>40.481783900000003</v>
       </c>
       <c r="AU50">
-        <v>-3.7185271</v>
+        <v>-3.7185271000000002</v>
       </c>
       <c r="AV50" t="s">
         <v>713</v>
@@ -14916,7 +14936,7 @@
         <v>0</v>
       </c>
       <c r="AZ50">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="BA50">
         <v>99</v>
@@ -15003,7 +15023,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="51" spans="1:111">
+    <row r="51" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>112</v>
       </c>
@@ -15083,10 +15103,10 @@
         <v>681</v>
       </c>
       <c r="AT51">
-        <v>40.4817839</v>
+        <v>40.481783900000003</v>
       </c>
       <c r="AU51">
-        <v>-3.7185271</v>
+        <v>-3.7185271000000002</v>
       </c>
       <c r="AV51" t="s">
         <v>713</v>
@@ -15098,7 +15118,7 @@
         <v>0</v>
       </c>
       <c r="AZ51">
-        <v>4.6</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="BA51">
         <v>99</v>
@@ -15185,7 +15205,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="52" spans="1:111">
+    <row r="52" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>112</v>
       </c>
@@ -15232,7 +15252,7 @@
         <v>390</v>
       </c>
       <c r="AT52">
-        <v>40.4644951</v>
+        <v>40.464495100000001</v>
       </c>
       <c r="AU52">
         <v>-3.7226857</v>
@@ -15292,7 +15312,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="53" spans="1:111">
+    <row r="53" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>112</v>
       </c>
@@ -15381,10 +15401,10 @@
         <v>672</v>
       </c>
       <c r="AT53">
-        <v>40.4284144</v>
+        <v>40.428414400000001</v>
       </c>
       <c r="AU53">
-        <v>-3.6957017</v>
+        <v>-3.6957016999999999</v>
       </c>
       <c r="AV53" t="s">
         <v>715</v>
@@ -15465,7 +15485,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="54" spans="1:111">
+    <row r="54" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>112</v>
       </c>
@@ -15554,7 +15574,7 @@
         <v>682</v>
       </c>
       <c r="AT54">
-        <v>40.4277516</v>
+        <v>40.427751600000001</v>
       </c>
       <c r="AU54">
         <v>-3.6818857</v>
@@ -15662,7 +15682,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="55" spans="1:111">
+    <row r="55" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>112</v>
       </c>
@@ -15754,10 +15774,10 @@
         <v>683</v>
       </c>
       <c r="AT55">
-        <v>40.3923334</v>
+        <v>40.392333399999998</v>
       </c>
       <c r="AU55">
-        <v>-3.7514199</v>
+        <v>-3.7514199000000001</v>
       </c>
       <c r="AV55" t="s">
         <v>717</v>
@@ -15871,7 +15891,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="56" spans="1:111">
+    <row r="56" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>112</v>
       </c>
@@ -15963,10 +15983,10 @@
         <v>684</v>
       </c>
       <c r="AT56">
-        <v>40.3923334</v>
+        <v>40.392333399999998</v>
       </c>
       <c r="AU56">
-        <v>-3.7514199</v>
+        <v>-3.7514199000000001</v>
       </c>
       <c r="AV56" t="s">
         <v>717</v>
@@ -16080,7 +16100,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="57" spans="1:111">
+    <row r="57" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>112</v>
       </c>
@@ -16172,10 +16192,10 @@
         <v>685</v>
       </c>
       <c r="AT57">
-        <v>40.3923334</v>
+        <v>40.392333399999998</v>
       </c>
       <c r="AU57">
-        <v>-3.7514199</v>
+        <v>-3.7514199000000001</v>
       </c>
       <c r="AV57" t="s">
         <v>717</v>
@@ -16289,7 +16309,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="58" spans="1:111">
+    <row r="58" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>112</v>
       </c>
@@ -16390,7 +16410,7 @@
         <v>40.4228977</v>
       </c>
       <c r="AU58">
-        <v>-3.6805261</v>
+        <v>-3.6805260999999998</v>
       </c>
       <c r="AV58" t="s">
         <v>718</v>
@@ -16402,7 +16422,7 @@
         <v>0</v>
       </c>
       <c r="AZ58">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="BA58">
         <v>236</v>
@@ -16543,7 +16563,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="59" spans="1:111">
+    <row r="59" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>112</v>
       </c>
@@ -16644,7 +16664,7 @@
         <v>40.4228977</v>
       </c>
       <c r="AU59">
-        <v>-3.6805261</v>
+        <v>-3.6805260999999998</v>
       </c>
       <c r="AV59" t="s">
         <v>718</v>
@@ -16656,7 +16676,7 @@
         <v>0</v>
       </c>
       <c r="AZ59">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="BA59">
         <v>236</v>
@@ -16797,7 +16817,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="60" spans="1:111">
+    <row r="60" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>112</v>
       </c>
@@ -16898,7 +16918,7 @@
         <v>40.4228977</v>
       </c>
       <c r="AU60">
-        <v>-3.6805261</v>
+        <v>-3.6805260999999998</v>
       </c>
       <c r="AV60" t="s">
         <v>718</v>
@@ -16910,7 +16930,7 @@
         <v>0</v>
       </c>
       <c r="AZ60">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="BA60">
         <v>236</v>
@@ -17051,7 +17071,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="61" spans="1:111">
+    <row r="61" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>112</v>
       </c>
@@ -17137,10 +17157,10 @@
         <v>679</v>
       </c>
       <c r="AT61">
-        <v>40.3907818</v>
+        <v>40.390781799999999</v>
       </c>
       <c r="AU61">
-        <v>-3.7285929</v>
+        <v>-3.7285929000000002</v>
       </c>
       <c r="AV61" t="s">
         <v>719</v>
@@ -17152,7 +17172,7 @@
         <v>0</v>
       </c>
       <c r="AZ61">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA61">
         <v>98</v>
@@ -17239,7 +17259,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="62" spans="1:111">
+    <row r="62" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>112</v>
       </c>
@@ -17328,10 +17348,10 @@
         <v>666</v>
       </c>
       <c r="AT62">
-        <v>40.4564523</v>
+        <v>40.456452300000002</v>
       </c>
       <c r="AU62">
-        <v>-3.6929304</v>
+        <v>-3.6929303999999998</v>
       </c>
       <c r="AV62" t="s">
         <v>702</v>
@@ -17424,7 +17444,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="63" spans="1:111">
+    <row r="63" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>112</v>
       </c>
@@ -17513,10 +17533,10 @@
         <v>667</v>
       </c>
       <c r="AT63">
-        <v>40.4564523</v>
+        <v>40.456452300000002</v>
       </c>
       <c r="AU63">
-        <v>-3.6929304</v>
+        <v>-3.6929303999999998</v>
       </c>
       <c r="AV63" t="s">
         <v>702</v>
@@ -17609,7 +17629,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="64" spans="1:111">
+    <row r="64" spans="1:111" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>112</v>
       </c>
@@ -17698,10 +17718,10 @@
         <v>668</v>
       </c>
       <c r="AT64">
-        <v>40.4564523</v>
+        <v>40.456452300000002</v>
       </c>
       <c r="AU64">
-        <v>-3.6929304</v>
+        <v>-3.6929303999999998</v>
       </c>
       <c r="AV64" t="s">
         <v>702</v>
@@ -17794,7 +17814,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="65" spans="1:112">
+    <row r="65" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>112</v>
       </c>
@@ -17889,10 +17909,10 @@
         <v>662</v>
       </c>
       <c r="AT65">
-        <v>40.4435437</v>
+        <v>40.443543699999999</v>
       </c>
       <c r="AU65">
-        <v>-3.6746052</v>
+        <v>-3.6746051999999998</v>
       </c>
       <c r="AV65" t="s">
         <v>720</v>
@@ -17904,7 +17924,7 @@
         <v>0</v>
       </c>
       <c r="AZ65">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA65">
         <v>93</v>
@@ -18009,7 +18029,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="66" spans="1:112">
+    <row r="66" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>112</v>
       </c>
@@ -18104,10 +18124,10 @@
         <v>663</v>
       </c>
       <c r="AT66">
-        <v>40.4435437</v>
+        <v>40.443543699999999</v>
       </c>
       <c r="AU66">
-        <v>-3.6746052</v>
+        <v>-3.6746051999999998</v>
       </c>
       <c r="AV66" t="s">
         <v>720</v>
@@ -18119,7 +18139,7 @@
         <v>0</v>
       </c>
       <c r="AZ66">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="BA66">
         <v>93</v>
@@ -18224,7 +18244,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="67" spans="1:112">
+    <row r="67" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>112</v>
       </c>
@@ -18313,7 +18333,7 @@
         <v>40.4271782</v>
       </c>
       <c r="AU67">
-        <v>-3.6698106</v>
+        <v>-3.6698105999999999</v>
       </c>
       <c r="AV67" t="s">
         <v>721</v>
@@ -18409,7 +18429,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="68" spans="1:112">
+    <row r="68" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>112</v>
       </c>
@@ -18456,10 +18476,10 @@
         <v>390</v>
       </c>
       <c r="AT68">
-        <v>40.3897989</v>
+        <v>40.389798900000002</v>
       </c>
       <c r="AU68">
-        <v>-3.6363388</v>
+        <v>-3.6363387999999999</v>
       </c>
       <c r="AV68" t="s">
         <v>722</v>
@@ -18555,7 +18575,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="69" spans="1:112">
+    <row r="69" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>112</v>
       </c>
@@ -18653,10 +18673,10 @@
         <v>686</v>
       </c>
       <c r="AT69">
-        <v>40.4050476</v>
+        <v>40.405047600000003</v>
       </c>
       <c r="AU69">
-        <v>-3.7974414</v>
+        <v>-3.7974413999999999</v>
       </c>
       <c r="AV69" t="s">
         <v>723</v>
@@ -18809,7 +18829,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="70" spans="1:112">
+    <row r="70" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>112</v>
       </c>
@@ -18907,10 +18927,10 @@
         <v>269</v>
       </c>
       <c r="AT70">
-        <v>40.4050476</v>
+        <v>40.405047600000003</v>
       </c>
       <c r="AU70">
-        <v>-3.7974414</v>
+        <v>-3.7974413999999999</v>
       </c>
       <c r="AV70" t="s">
         <v>723</v>
@@ -19063,7 +19083,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="71" spans="1:112">
+    <row r="71" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>112</v>
       </c>
@@ -19161,10 +19181,10 @@
         <v>687</v>
       </c>
       <c r="AT71">
-        <v>40.4050476</v>
+        <v>40.405047600000003</v>
       </c>
       <c r="AU71">
-        <v>-3.7974414</v>
+        <v>-3.7974413999999999</v>
       </c>
       <c r="AV71" t="s">
         <v>723</v>
@@ -19317,7 +19337,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="72" spans="1:112">
+    <row r="72" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>112</v>
       </c>
@@ -19418,10 +19438,10 @@
         <v>688</v>
       </c>
       <c r="AT72">
-        <v>40.4257227</v>
+        <v>40.425722700000001</v>
       </c>
       <c r="AU72">
-        <v>-3.6734007</v>
+        <v>-3.6734007000000002</v>
       </c>
       <c r="AV72" t="s">
         <v>724</v>
@@ -19433,7 +19453,7 @@
         <v>0</v>
       </c>
       <c r="AZ72">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="BA72">
         <v>372</v>
@@ -19577,7 +19597,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="73" spans="1:112">
+    <row r="73" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>112</v>
       </c>
@@ -19678,10 +19698,10 @@
         <v>658</v>
       </c>
       <c r="AT73">
-        <v>40.4257227</v>
+        <v>40.425722700000001</v>
       </c>
       <c r="AU73">
-        <v>-3.6734007</v>
+        <v>-3.6734007000000002</v>
       </c>
       <c r="AV73" t="s">
         <v>724</v>
@@ -19693,7 +19713,7 @@
         <v>0</v>
       </c>
       <c r="AZ73">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="BA73">
         <v>372</v>
@@ -19837,7 +19857,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="74" spans="1:112">
+    <row r="74" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>112</v>
       </c>
@@ -19938,10 +19958,10 @@
         <v>658</v>
       </c>
       <c r="AT74">
-        <v>40.4257227</v>
+        <v>40.425722700000001</v>
       </c>
       <c r="AU74">
-        <v>-3.6734007</v>
+        <v>-3.6734007000000002</v>
       </c>
       <c r="AV74" t="s">
         <v>724</v>
@@ -19953,7 +19973,7 @@
         <v>0</v>
       </c>
       <c r="AZ74">
-        <v>4.4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="BA74">
         <v>372</v>
@@ -20097,7 +20117,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="75" spans="1:112">
+    <row r="75" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>112</v>
       </c>
@@ -20201,7 +20221,7 @@
         <v>40.435983</v>
       </c>
       <c r="AU75">
-        <v>-3.642721</v>
+        <v>-3.6427209999999999</v>
       </c>
       <c r="AV75" t="s">
         <v>725</v>
@@ -20357,7 +20377,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="76" spans="1:112">
+    <row r="76" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>112</v>
       </c>
@@ -20461,7 +20481,7 @@
         <v>40.435983</v>
       </c>
       <c r="AU76">
-        <v>-3.642721</v>
+        <v>-3.6427209999999999</v>
       </c>
       <c r="AV76" t="s">
         <v>725</v>
@@ -20617,7 +20637,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="77" spans="1:112">
+    <row r="77" spans="1:112" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>112</v>
       </c>
@@ -20721,7 +20741,7 @@
         <v>40.435983</v>
       </c>
       <c r="AU77">
-        <v>-3.642721</v>
+        <v>-3.6427209999999999</v>
       </c>
       <c r="AV77" t="s">
         <v>725</v>
@@ -20875,6 +20895,282 @@
       </c>
       <c r="DH77" t="s">
         <v>1397</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:DH77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9853003F-96AF-4C36-AF28-1F88C53C536C}">
+  <dimension ref="A1:A54"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>576</v>
       </c>
     </row>
   </sheetData>
